--- a/tests/fixtures/test_cases/t101_perfect_fr.xlsx
+++ b/tests/fixtures/test_cases/t101_perfect_fr.xlsx
@@ -413,94 +413,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Population (en milliers)</t>
+          <t>Emploi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Biens</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15996.7</v>
+        <v>4500.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Québec</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9024.9</v>
+        <v>15500.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colombie-Britannique</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5640.8</v>
+        <v>20000.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alberta</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4850.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Source : Statistique Canada, Division de la démographie, T2 2026.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>x confidentiel</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>.. non disponible</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>..</t>
+          <t>Source : Statistique Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/test_cases/t101_perfect_fr.xlsx
+++ b/tests/fixtures/test_cases/t101_perfect_fr.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,60 +417,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Province</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Emploi</t>
+          <t>Population (en milliers)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Biens</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4500.2</v>
+        <v>15996.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Québec</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15500.6</v>
+        <v>9024.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Colombie-Britannique</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20000.8</v>
+        <v>5640.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Source : Statistique Canada</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>confidentiel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Source : Statistique Canada, Division de la démographie, T2 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>.. non disponible</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Note : x = confidentiel; .. = non disponible. Données désaisonnalisées.</t>
         </is>
       </c>
     </row>
